--- a/src/assets/template/Client.xlsx
+++ b/src/assets/template/Client.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a7ef8c62264e85ff/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesld\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3D28DE6-3C62-42E1-80E0-5744089D0662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD3AEFC-0DC6-4138-9911-21DE060DCCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1193D5F1-C798-48BE-B22D-5C01532F52FC}"/>
   </bookViews>
@@ -34,14 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Sr No</t>
   </si>
   <si>
-    <t>Manager</t>
-  </si>
-  <si>
     <t>Client Name</t>
   </si>
   <si>
@@ -99,9 +96,6 @@
     <t>Contact Person 3 Email</t>
   </si>
   <si>
-    <t>Emails</t>
-  </si>
-  <si>
     <t>Start Date</t>
   </si>
   <si>
@@ -112,16 +106,156 @@
   </si>
   <si>
     <t>Tax Payable</t>
+  </si>
+  <si>
+    <t>Society Manager</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Note -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GST Applicable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tax Payable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> required then type </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Yes"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and If not required, type</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"No" || </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Emails should be separated by commas</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (,)</t>
+    </r>
+  </si>
+  <si>
+    <t>Other Emails</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -463,9 +597,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5B2CC56-B6F9-4F1A-A714-5A5638ED1F2E}">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="32.77734375" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" customWidth="1"/>
     <col min="3" max="4" width="13.5546875" customWidth="1"/>
     <col min="6" max="6" width="16.77734375" customWidth="1"/>
@@ -482,84 +617,89 @@
     <col min="26" max="26" width="11.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O2" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P2" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q2" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R2" t="s">
         <v>15</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S2" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U2" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V2" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" t="s">
         <v>20</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y2" t="s">
         <v>21</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z2" t="s">
         <v>22</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/template/Client.xlsx
+++ b/src/assets/template/Client.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesld\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Angular_Workspace\taskappnew\src\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD3AEFC-0DC6-4138-9911-21DE060DCCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6509B0-C682-45A5-84E9-D6A53F105C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1193D5F1-C798-48BE-B22D-5C01532F52FC}"/>
   </bookViews>
@@ -108,9 +108,6 @@
     <t>Tax Payable</t>
   </si>
   <si>
-    <t>Society Manager</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -230,6 +227,9 @@
   </si>
   <si>
     <t>Other Emails</t>
+  </si>
+  <si>
+    <t>Society Manager Email</t>
   </si>
 </sst>
 </file>
@@ -619,7 +619,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
@@ -627,7 +627,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>19</v>
       </c>
       <c r="W2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X2" t="s">
         <v>20</v>
